--- a/AAII_Financials/Yearly/FDX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FDX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>FDX</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E7" s="2">
         <v>45808</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45443</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45077</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44712</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44347</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43982</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43616</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43251</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42886</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42521</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42155</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41790</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41425</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>41060</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>94720000</v>
+      </c>
+      <c r="E8" s="3">
         <v>87926000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>87693000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>90155000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>93512000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>83959000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>69217000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>69693000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>65450000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>60319000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>50365000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>47453000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>45567000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>44287000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>42680000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>68844000</v>
+      </c>
+      <c r="E9" s="3">
         <v>63954000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>63732000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>65759000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>70101000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>60229000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>52380000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>54764000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>47445000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16403000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12365000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12203000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12568000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12018000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>11291000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>25876000</v>
+      </c>
+      <c r="E10" s="3">
         <v>23972000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>23961000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24396000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>23411000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>23730000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>16837000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>14929000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>18005000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>43916000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>38000000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>35250000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>32999000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>32269000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>31389000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,105 +998,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>833000</v>
+        <v>1133000</v>
       </c>
       <c r="E14" s="3">
-        <v>682000</v>
+        <v>815000</v>
       </c>
       <c r="F14" s="3">
+        <v>739000</v>
+      </c>
+      <c r="G14" s="3">
         <v>426000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>278000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>509000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>435000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>366000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>590000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>276000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>660000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>134000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4369000</v>
+      </c>
+      <c r="E15" s="3">
         <v>4264000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4287000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4176000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3970000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3793000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3615000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3353000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3095000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2995000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2631000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2611000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2587000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2386000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2113000</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>87245000</v>
+      </c>
+      <c r="E17" s="3">
         <v>81181000</v>
       </c>
-      <c r="E17" s="3">
-        <v>80730000</v>
-      </c>
       <c r="F17" s="3">
+        <v>80673000</v>
+      </c>
+      <c r="G17" s="3">
         <v>83763000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>87715000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>76003000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>66487000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>68112000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>59990000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>55753000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>47288000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>45586000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>41752000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>39853000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>39494000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7475000</v>
+      </c>
+      <c r="E18" s="3">
         <v>6745000</v>
       </c>
-      <c r="E18" s="3">
-        <v>6963000</v>
-      </c>
       <c r="F18" s="3">
+        <v>7020000</v>
+      </c>
+      <c r="G18" s="3">
         <v>6392000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5797000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7956000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2730000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1581000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5460000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4566000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3077000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1867000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3815000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4434000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3186000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>45000</v>
+        <v>16000</v>
       </c>
       <c r="E20" s="3">
+        <v>63000</v>
+      </c>
+      <c r="F20" s="3">
         <v>70000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>107000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-13000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>32000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>9000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>31000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1037000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>10964000</v>
+        <v>11828000</v>
       </c>
       <c r="E21" s="3">
-        <v>11180000</v>
+        <v>10946000</v>
       </c>
       <c r="F21" s="3">
+        <v>11237000</v>
+      </c>
+      <c r="G21" s="3">
         <v>10461000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9780000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11717000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6336000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4903000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8548000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8598000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5707000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4473000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6405000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6806000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5306000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>970000</v>
+      </c>
+      <c r="E22" s="3">
         <v>789000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>745000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>694000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>689000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>793000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>672000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>588000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>558000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1024000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>336000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>235000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>160000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>82000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>52000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5793000</v>
+      </c>
+      <c r="E23" s="3">
         <v>5441000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5836000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5363000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4896000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6674000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1669000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>655000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4353000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4579000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2740000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1627000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3658000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4338000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3141000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1360000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1349000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1505000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1391000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1070000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1443000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>383000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>115000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-219000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1582000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>920000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>577000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1334000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1622000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1109000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4433000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4092000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4331000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3972000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3826000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5231000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1286000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>540000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4572000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2997000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1820000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1050000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2324000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2716000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2032000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4426000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4087000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4325000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3966000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3819000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5220000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1284000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>539000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4566000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2993000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1818000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1048000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2320000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2711000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2032000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1673,8 +1733,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-45000</v>
+        <v>-16000</v>
       </c>
       <c r="E32" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-70000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-107000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>13000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-32000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-9000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-31000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1037000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>14000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4433000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4092000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4331000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3972000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3826000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5231000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1286000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>540000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4572000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2993000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1818000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1048000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2320000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2711000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2032000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4433000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4092000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4331000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3972000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3826000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5231000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1286000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>540000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4572000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2993000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1818000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1048000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2320000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2711000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2032000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E38" s="2">
         <v>45808</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45443</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45077</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44712</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44347</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43982</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43616</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43251</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42886</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42521</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42155</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41790</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41425</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>41060</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,71 +2158,75 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13311000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5502000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6501000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6856000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6897000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7087000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4881000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2319000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3265000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3969000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3534000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3763000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2908000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4917000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2843000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>240000</v>
+      </c>
+      <c r="E42" s="3">
         <v>70000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>77000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>302000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -2168,116 +2257,125 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12672000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11368000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10087000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10188000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11863000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12069000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10102000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9116000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8481000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7599000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7252000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5719000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5460000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5044000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4704000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>669000</v>
+      </c>
+      <c r="E44" s="3">
         <v>602000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>614000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>604000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>637000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>587000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>572000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>553000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>525000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>514000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>496000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>498000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>463000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>457000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>440000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E45" s="3">
         <v>13000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8000</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>8</v>
@@ -2294,86 +2392,92 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>546000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>707000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>961000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>852000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>856000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1069000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>27903000</v>
+      </c>
+      <c r="E46" s="3">
         <v>18386000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18207000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18610000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>20365000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>20580000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16383000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13086000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13341000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12628000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11989000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10335000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9683000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11274000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9056000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>564000</v>
+      </c>
+      <c r="E47" s="3">
         <v>506000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>360000</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
@@ -2390,123 +2494,132 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>729000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>413000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>472000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>396000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>414000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>661000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>58866000</v>
+      </c>
+      <c r="E48" s="3">
         <v>58095000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>58606000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>58045000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>54704000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>51135000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>47525000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>30429000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>28154000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25981000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>71302000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20875000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19550000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>18484000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17248000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6886000</v>
+      </c>
+      <c r="E49" s="3">
         <v>6808000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6604000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6669000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6845000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7314000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6694000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7300000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7453000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7683000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7755000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4224000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2954000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2827000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2421000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3561000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2716000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1917000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2656000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2873000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2330000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1588000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2248000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2119000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1531000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4870000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1304000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>883000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>568000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>517000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>98937000</v>
+      </c>
+      <c r="E54" s="3">
         <v>87627000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>87007000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>87143000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>85994000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>82777000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>73537000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>54403000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>52330000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>48552000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>45959000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36531000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33070000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>33567000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>29903000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,104 +2914,111 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4327000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3692000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3189000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3848000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4030000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3841000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3269000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3030000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2977000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2752000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2944000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2066000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1971000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1879000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1613000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5102000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3993000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2531000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2516000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2525000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2354000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1974000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>964000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1342000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>22000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>29000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>19000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>251000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>417000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2890,10 +3026,10 @@
         <v>23000</v>
       </c>
       <c r="E59" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F59" s="3">
         <v>23000</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>8</v>
@@ -2910,171 +3046,183 @@
       <c r="K59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3">
         <v>5144000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10070000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6307000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3340000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3620000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3344000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18912000</v>
+      </c>
+      <c r="E60" s="3">
         <v>15411000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13355000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13586000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14274000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13660000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10344000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9013000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9627000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7918000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8008000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5956000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5312000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5750000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5374000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>37842000</v>
+      </c>
+      <c r="E61" s="3">
         <v>33423000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>35188000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>35816000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>34669000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>34108000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>34147000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16617000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15243000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14909000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13733000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7249000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4736000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2739000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1250000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5247000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4816000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4390000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4034000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3571000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3413000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2570000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3100000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2869000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9652000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10434000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8333000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7745000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7680000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8552000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>67290000</v>
+      </c>
+      <c r="E66" s="3">
         <v>59553000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>59425000</v>
-      </c>
-      <c r="F66" s="3">
-        <v>61055000</v>
       </c>
       <c r="G66" s="3">
         <v>61055000</v>
       </c>
       <c r="H66" s="3">
+        <v>61055000</v>
+      </c>
+      <c r="I66" s="3">
         <v>58609000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>55242000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>36646000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32914000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>32479000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>32175000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>21538000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17793000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16169000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15176000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>44461000</v>
+      </c>
+      <c r="E72" s="3">
         <v>41402000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>38649000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>35259000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>32782000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>29817000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>25216000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>24648000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>24823000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20833000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18371000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16900000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16229000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>18519000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17134000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>31647000</v>
+      </c>
+      <c r="E76" s="3">
         <v>28074000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>27582000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26088000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>24939000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>24168000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18295000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17757000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19416000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16073000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13784000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14993000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15277000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17398000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14727000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E80" s="2">
         <v>45808</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45443</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45077</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44712</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44347</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43982</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43616</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43251</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42886</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42521</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42155</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41790</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41425</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>41060</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4433000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4092000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4331000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3972000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3826000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5231000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1286000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>540000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4572000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2993000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1818000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1048000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2320000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2711000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2032000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4315000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4216000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4240000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4124000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3918000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3744000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3549000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3271000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3008000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2995000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2631000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2611000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2587000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2386000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2113000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8925000</v>
+      </c>
+      <c r="E89" s="3">
         <v>7036000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8312000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8848000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9832000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10135000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5097000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5613000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4674000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4930000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5708000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5366000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4264000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4688000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4835000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3809000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4055000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5176000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6174000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6763000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5884000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5868000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5490000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5663000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5116000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4828000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4347000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3533000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3375000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4007000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3911000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4092000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5200000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6174000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6816000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6010000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5846000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5473000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5677000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4981000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9446000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5752000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3551000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3803000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4049000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1374000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1339000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1259000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1177000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>793000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>686000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>679000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>683000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>535000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-426000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-277000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-227000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-187000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-177000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-164000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2749000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4019000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3426000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2597000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3019000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2090000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3381000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1039000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>227000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>528000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3611000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1349000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2719000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1184000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-244000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E101" s="3">
         <v>76000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-41000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-118000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-187000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>171000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-70000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-47000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>72000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-42000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-102000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-108000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>5000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-27000</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7809000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-999000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-355000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-41000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-190000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2206000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2562000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-946000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-704000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>435000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-229000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>855000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2009000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2074000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>515000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
